--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA4A252-4A61-4D03-9632-A8DED8E614FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13699D1D-97A2-49A5-A274-049F105DC149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -89,6 +89,34 @@
   </si>
   <si>
     <t>User should successfully login and be redirected to the home page.</t>
+  </si>
+  <si>
+    <t>User logged in successfully and was redirected to the home page.</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>TS-003</t>
+  </si>
+  <si>
+    <t>Verify login fails when an incorrect password is entered.</t>
+  </si>
+  <si>
+    <t>1. Open the ShopEase Login page.
+2. Enter a valid email address.
+3. Enter an incorrect password.
+4. Click the Login button.</t>
+  </si>
+  <si>
+    <t>Email: demo@example.com
+Password: WrongPassword123</t>
+  </si>
+  <si>
+    <t>The system should reject the login attempt and display an appropriate error message.</t>
   </si>
 </sst>
 </file>
@@ -449,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -462,7 +490,7 @@
     <col min="8" max="8" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -494,7 +522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -516,8 +544,43 @@
       <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
     </row>
   </sheetData>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13699D1D-97A2-49A5-A274-049F105DC149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23D3C53-646A-49A4-9766-95BAE7DDF2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -117,6 +117,34 @@
   </si>
   <si>
     <t>The system should reject the login attempt and display an appropriate error message.</t>
+  </si>
+  <si>
+    <t>Error displayed</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>TS-002</t>
+  </si>
+  <si>
+    <t>Verify login validation when email is empty.</t>
+  </si>
+  <si>
+    <t>1. Open the ShopEase Login page.
+2. Leave the email field empty.
+3. Enter a valid password.
+4. Click the Login button.</t>
+  </si>
+  <si>
+    <t>Email: [Empty]
+Password: Password123</t>
+  </si>
+  <si>
+    <t>The system should display "Email is required."</t>
+  </si>
+  <si>
+    <t>Email validation</t>
   </si>
 </sst>
 </file>
@@ -573,12 +601,45 @@
       <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23D3C53-646A-49A4-9766-95BAE7DDF2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EBD021-5FD2-4F07-AB2E-D2BFA94328FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EBD021-5FD2-4F07-AB2E-D2BFA94328FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2306AE5-1BC8-478B-8B96-A80D1AD95BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -145,6 +145,24 @@
   </si>
   <si>
     <t>Email validation</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>Verify validation when the password field is empty</t>
+  </si>
+  <si>
+    <t>User is on the Login page</t>
+  </si>
+  <si>
+    <t>Email: demo@example.com Password: Empty</t>
+  </si>
+  <si>
+    <t>Login should not proceed. The message "Password is required." should be displayed.</t>
+  </si>
+  <si>
+    <t>1. Enter valid email. 2. Leave Password empty.                      3. Click Login.</t>
   </si>
 </sst>
 </file>
@@ -180,11 +198,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -551,98 +566,118 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
+    <row r="5" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2306AE5-1BC8-478B-8B96-A80D1AD95BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC68C76-D055-4D34-9CF7-1E193F28D860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>1. Enter valid email. 2. Leave Password empty.                      3. Click Login.</t>
+  </si>
+  <si>
+    <t>Login was not allowed when the password field was left empty. The message “Password is required.” was displayed</t>
   </si>
 </sst>
 </file>
@@ -198,13 +201,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,7 +536,7 @@
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="18.88671875" customWidth="1"/>
     <col min="7" max="7" width="21.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -656,7 +662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -677,9 +683,16 @@
       </c>
       <c r="G5" s="2" t="s">
         <v>37</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC68C76-D055-4D34-9CF7-1E193F28D860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDD3BB4-179D-4CB7-987D-835790960C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -166,19 +166,105 @@
   </si>
   <si>
     <t>Login was not allowed when the password field was left empty. The message “Password is required.” was displayed</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>Verify validation when an invalid email format is entered</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Email: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>demo@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Password: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Password123</t>
+    </r>
+  </si>
+  <si>
+    <t>Login should not proceed. The message "Please enter a valid email address." should be displayed.</t>
+  </si>
+  <si>
+    <r>
+      <t>Login was not allowed when an invalid email format (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>demo@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) was entered. The message “Please enter a valid email address.” was displayed.</t>
+    </r>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>Verify validation when both email and password are empty</t>
+  </si>
+  <si>
+    <t>1. Leave Email empty.                                              2. Leave Password empty.                                              3. Click Login.</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid email.                       2. Enter a valid password.                 3. Click Login.</t>
+  </si>
+  <si>
+    <t>Email: Empty; Password: Empty</t>
+  </si>
+  <si>
+    <t>Login should not proceed. Appropriate validation messages should be displayed for both required fields.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -526,8 +612,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
@@ -539,7 +625,7 @@
     <col min="8" max="8" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -571,7 +657,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="115.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -600,7 +686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="115.2">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -633,7 +719,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="115.2">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -662,7 +748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="129.6">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -689,6 +775,58 @@
       </c>
       <c r="I5" s="1" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="158.4">
+      <c r="A6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="72">
+      <c r="A7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDD3BB4-179D-4CB7-987D-835790960C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D937C6EB-706D-40A7-9410-4E48A2F3D490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -247,6 +247,52 @@
   </si>
   <si>
     <t>Login should not proceed. Appropriate validation messages should be displayed for both required fields.</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>Verify password minimum-length boundary</t>
+  </si>
+  <si>
+    <t>User is on the Login or Registration page where the minimum password rule is applicable</t>
+  </si>
+  <si>
+    <t>1. Enter a password containing 7 characters.               2. Submit the form.  3. Verify validation.  4. Enter a password containing exactly 8 characters.               5. Submit the form.  6. Verify validation.</t>
+  </si>
+  <si>
+    <t>7-character password should be rejected. 8-character password should satisfy the minimum-length requirement.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7 characters: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Pass123</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                    8 characters: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Pass1234</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -612,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -829,6 +875,29 @@
         <v>50</v>
       </c>
     </row>
+    <row r="8" spans="1:13" ht="144">
+      <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D937C6EB-706D-40A7-9410-4E48A2F3D490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E777BD-258D-4B97-81AE-8EF4DDABBB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="67">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -293,6 +293,74 @@
       </rPr>
       <t>Pass1234</t>
     </r>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>TS-004</t>
+  </si>
+  <si>
+    <t>Verify Remember Me behavior during login</t>
+  </si>
+  <si>
+    <t>User is on the Login page and is logged out</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Email: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>demo@example.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Password: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Password123</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Remember Me: Checked</t>
+    </r>
+  </si>
+  <si>
+    <t>When Remember Me is selected, the application should maintain the intended login/session state according to the application's requirements.</t>
+  </si>
+  <si>
+    <t>1. Enter valid email. 2. Enter valid password.                 3. Select Remember Me.                           4. Click Login.            5. Close the browser/page.            6. Reopen the ShopEase application. 7. Observe the login/session state.</t>
+  </si>
+  <si>
+    <t>User remained logged in after reopening the website. The Home page displayed Profile and Logout options.</t>
+  </si>
+  <si>
+    <t>A 7-character password was rejected, while an 8-character password was accepted as satisfying the minimum password-length requirement.</t>
+  </si>
+  <si>
+    <t>Login was not allowed when both Email and Password fields were empty. The required validation messages for both fields were displayed.</t>
   </si>
 </sst>
 </file>
@@ -658,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -852,7 +920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="72">
+    <row r="7" spans="1:13" ht="144">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
@@ -874,8 +942,14 @@
       <c r="G7" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="H7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" ht="144">
+    <row r="8" spans="1:13" ht="158.4">
       <c r="A8" s="1" t="s">
         <v>51</v>
       </c>
@@ -896,6 +970,41 @@
       </c>
       <c r="G8" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="172.8">
+      <c r="A9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E777BD-258D-4B97-81AE-8EF4DDABBB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E06691-468B-41BF-8F4C-707EA0074A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -361,13 +361,19 @@
   </si>
   <si>
     <t>Login was not allowed when both Email and Password fields were empty. The required validation messages for both fields were displayed.</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Products</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,6 +385,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -401,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -411,6 +425,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -726,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -771,243 +788,275 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="115.2">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
-      </c>
+    <row r="2" spans="1:13">
+      <c r="A2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:13" ht="115.2">
-      <c r="A3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="115.2">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="129.6">
-      <c r="A5" s="1" t="s">
-        <v>33</v>
+    <row r="5" spans="1:13" ht="115.2">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="129.6">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="158.4">
-      <c r="A6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="144">
+    <row r="7" spans="1:13" ht="158.4">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="158.4">
+    <row r="8" spans="1:13" ht="144">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="172.8">
+    <row r="9" spans="1:13" ht="158.4">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="10" spans="1:13" ht="172.8">
+      <c r="A10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E06691-468B-41BF-8F4C-707EA0074A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A345C30-1B10-47EA-9664-FD0C8F46AEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="85">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -367,6 +367,54 @@
   </si>
   <si>
     <t>Products</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>TS-005</t>
+  </si>
+  <si>
+    <t>Verify that users can view available products</t>
+  </si>
+  <si>
+    <t>ShopEase is open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Products.  2. Observe the product listing      </t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>The product listing should display products with their names, prices, images, and other available information.</t>
+  </si>
+  <si>
+    <t>Products were displayed with their names, prices, and images.</t>
+  </si>
+  <si>
+    <t>TS-006</t>
+  </si>
+  <si>
+    <t>Verify that users can search for an existing product</t>
+  </si>
+  <si>
+    <t>Products page is open</t>
+  </si>
+  <si>
+    <t>1. Enter an existing product name in the search box. 2. Click Search or press Enter.</t>
+  </si>
+  <si>
+    <t>Headphones</t>
+  </si>
+  <si>
+    <t>Matching product(s) should be displayed.</t>
+  </si>
+  <si>
+    <t>Matching product(s) were displayed for the entered product name.</t>
   </si>
 </sst>
 </file>
@@ -743,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -1052,6 +1100,64 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:J2"/>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A345C30-1B10-47EA-9664-FD0C8F46AEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A676514-6B67-4090-842C-831FD550A738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="141">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -160,9 +160,6 @@
   </si>
   <si>
     <t>Login should not proceed. The message "Password is required." should be displayed.</t>
-  </si>
-  <si>
-    <t>1. Enter valid email. 2. Leave Password empty.                      3. Click Login.</t>
   </si>
   <si>
     <t>Login was not allowed when the password field was left empty. The message “Password is required.” was displayed</t>
@@ -240,9 +237,6 @@
     <t>1. Leave Email empty.                                              2. Leave Password empty.                                              3. Click Login.</t>
   </si>
   <si>
-    <t>1. Enter an invalid email.                       2. Enter a valid password.                 3. Click Login.</t>
-  </si>
-  <si>
     <t>Email: Empty; Password: Empty</t>
   </si>
   <si>
@@ -256,9 +250,6 @@
   </si>
   <si>
     <t>User is on the Login or Registration page where the minimum password rule is applicable</t>
-  </si>
-  <si>
-    <t>1. Enter a password containing 7 characters.               2. Submit the form.  3. Verify validation.  4. Enter a password containing exactly 8 characters.               5. Submit the form.  6. Verify validation.</t>
   </si>
   <si>
     <t>7-character password should be rejected. 8-character password should satisfy the minimum-length requirement.</t>
@@ -351,9 +342,6 @@
     <t>When Remember Me is selected, the application should maintain the intended login/session state according to the application's requirements.</t>
   </si>
   <si>
-    <t>1. Enter valid email. 2. Enter valid password.                 3. Select Remember Me.                           4. Click Login.            5. Close the browser/page.            6. Reopen the ShopEase application. 7. Observe the login/session state.</t>
-  </si>
-  <si>
     <t>User remained logged in after reopening the website. The Home page displayed Profile and Logout options.</t>
   </si>
   <si>
@@ -384,9 +372,6 @@
     <t>ShopEase is open</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click Products.  2. Observe the product listing      </t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -405,9 +390,6 @@
     <t>Products page is open</t>
   </si>
   <si>
-    <t>1. Enter an existing product name in the search box. 2. Click Search or press Enter.</t>
-  </si>
-  <si>
     <t>Headphones</t>
   </si>
   <si>
@@ -415,6 +397,192 @@
   </si>
   <si>
     <t>Matching product(s) were displayed for the entered product name.</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>Verify the result when searching for a product that does not exist</t>
+  </si>
+  <si>
+    <t>No products should match. A suitable “No products found” message should appear, or the empty results state should be clearly indicated.</t>
+  </si>
+  <si>
+    <t>No matching products were displayed, and the empty results state was shown.</t>
+  </si>
+  <si>
+    <t>NonExistingProduct0</t>
+  </si>
+  <si>
+    <t>TC-012</t>
+  </si>
+  <si>
+    <t>Verify that product search works regardless of letter case</t>
+  </si>
+  <si>
+    <t>HEADPHONES</t>
+  </si>
+  <si>
+    <t>The matching product should be displayed regardless of letter case.</t>
+  </si>
+  <si>
+    <t>The matching product was displayed when the product name was searched using uppercase letters.</t>
+  </si>
+  <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>TS-007</t>
+  </si>
+  <si>
+    <t>Verify that selecting a category filters the product listing</t>
+  </si>
+  <si>
+    <t>Products page is open and category filters are available</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Only products belonging to the selected category should be displayed.</t>
+  </si>
+  <si>
+    <t>Only products belonging to the selected category were displayed.</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>TS-008</t>
+  </si>
+  <si>
+    <t>Verify that products can be sorted by price from low to high</t>
+  </si>
+  <si>
+    <t>Products page contains multiple products</t>
+  </si>
+  <si>
+    <t>Sort option: Price Low to High</t>
+  </si>
+  <si>
+    <t>Products should appear in ascending price order.</t>
+  </si>
+  <si>
+    <t>Products were displayed in ascending price order, from lowest to highest price.</t>
+  </si>
+  <si>
+    <t>TC-015</t>
+  </si>
+  <si>
+    <t>Verify that products can be sorted by price from high to low</t>
+  </si>
+  <si>
+    <t>Sort option: Price High to Low</t>
+  </si>
+  <si>
+    <t>Products should appear in descending price order.</t>
+  </si>
+  <si>
+    <t>Products were displayed in descending price order, from highest to lowest price.</t>
+  </si>
+  <si>
+    <t>TC-016</t>
+  </si>
+  <si>
+    <t>Verify that products can be sorted by rating</t>
+  </si>
+  <si>
+    <t>Products page contains products with ratings and a rating sort option</t>
+  </si>
+  <si>
+    <t>Sort by Rating</t>
+  </si>
+  <si>
+    <t>Products should be sorted according to the selected rating order. If the option is highest rating first, ratings should be in descending order.</t>
+  </si>
+  <si>
+    <t>Products were displayed in the selected rating order.</t>
+  </si>
+  <si>
+    <t>TC-017</t>
+  </si>
+  <si>
+    <t>TS-009</t>
+  </si>
+  <si>
+    <t>Verify that users can open a product's details page</t>
+  </si>
+  <si>
+    <t>Any existing product</t>
+  </si>
+  <si>
+    <t>The details page should display the correct product name, image, price, description, and availability information where provided.</t>
+  </si>
+  <si>
+    <t>The product details page opened and displayed the selected product's information correctly.</t>
+  </si>
+  <si>
+    <t>TC-018</t>
+  </si>
+  <si>
+    <t>TS-010</t>
+  </si>
+  <si>
+    <t>Verify that an out-of-stock product cannot be added to the cart</t>
+  </si>
+  <si>
+    <t>At least one product is marked out of stock</t>
+  </si>
+  <si>
+    <t>An out-of-stock product in ShopEase</t>
+  </si>
+  <si>
+    <t>The product should be clearly marked out of stock and should not be added to the cart.</t>
+  </si>
+  <si>
+    <t>The product was marked out of stock and could not be added to the cart</t>
+  </si>
+  <si>
+    <t>1. Search for an existing product using uppercase letters.                      2. Observe the results.</t>
+  </si>
+  <si>
+    <t>1. Select the rating sort option.                  2. Compare product ratings from top to bottom.</t>
+  </si>
+  <si>
+    <t>1. Open an out-of-stock product.             2. Check its availability.                  3. Attempt to add it to the cart, if the control is available.                  4. Check the cart.</t>
+  </si>
+  <si>
+    <t>1. Click a product or its View Details button.                              2. Inspect the product details page.</t>
+  </si>
+  <si>
+    <t>1. Select Price: High to Low.                                2. Compare the displayed prices from top to bottom.</t>
+  </si>
+  <si>
+    <t>1. Select Price: Low to High.                              2. Compare the displayed prices from top to bottom.</t>
+  </si>
+  <si>
+    <t>1. Enter valid email.   2. Leave Password empty.                          3. Click Login.</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid email.                            2. Enter a valid password.                    3. Click Login.</t>
+  </si>
+  <si>
+    <t>1. Enter a password containing 7 characters.                  2. Submit the form.    3. Verify validation.    4. Enter a password containing exactly 8 characters.                  5. Submit the form.    6. Verify validation.</t>
+  </si>
+  <si>
+    <t>1. Enter valid email.   2. Enter valid password.                    3. Select Remember Me.                                4. Click Login.              5. Close the browser/page.            6. Reopen the ShopEase application. 7. Observe the login/session state.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Products.        2. Observe the product listing      </t>
+  </si>
+  <si>
+    <t>1. Enter an existing product name in the search box.                  2. Click Search or press Enter.</t>
+  </si>
+  <si>
+    <t>1. Enter a product name that does not exist.                             2. Submit the search.</t>
+  </si>
+  <si>
+    <t>1. Select a category, such as Electronics.   2. Observe the product listing.</t>
   </si>
 </sst>
 </file>
@@ -791,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -838,7 +1006,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -955,7 +1123,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>36</v>
@@ -964,7 +1132,7 @@
         <v>37</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>18</v>
@@ -972,28 +1140,28 @@
     </row>
     <row r="7" spans="1:13" ht="158.4">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>18</v>
@@ -1001,28 +1169,28 @@
     </row>
     <row r="8" spans="1:13" ht="144">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>18</v>
@@ -1030,28 +1198,28 @@
     </row>
     <row r="9" spans="1:13" ht="158.4">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>18</v>
@@ -1059,28 +1227,28 @@
     </row>
     <row r="10" spans="1:13" ht="172.8">
       <c r="A10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="E10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>18</v>
@@ -1088,7 +1256,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1100,63 +1268,339 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
+    <row r="12" spans="1:13" ht="72">
+      <c r="A12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B12" t="s">
+      <c r="G12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C12" t="s">
+      <c r="H12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D12" t="s">
+      <c r="I12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="72">
+      <c r="A13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E12" t="s">
+      <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F12" t="s">
+      <c r="D13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G12" t="s">
+      <c r="E13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H12" t="s">
+      <c r="G13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="H13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C13" t="s">
+      <c r="I13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="100.8">
+      <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D13" t="s">
+      <c r="B14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="I14" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="115.2">
+      <c r="A15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I13" t="s">
-        <v>18</v>
-      </c>
+      <c r="B15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="72">
+      <c r="A16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="86.4">
+      <c r="A17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="86.4">
+      <c r="A18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="100.8">
+      <c r="A19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="115.2">
+      <c r="A20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="115.2">
+      <c r="A21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A676514-6B67-4090-842C-831FD550A738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909AE27F-81EC-4591-B871-F059F110CAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909AE27F-81EC-4591-B871-F059F110CAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B3B503-3D02-487C-A29A-F425B79149E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="188">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -584,12 +584,153 @@
   <si>
     <t>1. Select a category, such as Electronics.   2. Observe the product listing.</t>
   </si>
+  <si>
+    <t>Cart</t>
+  </si>
+  <si>
+    <t>TC-019</t>
+  </si>
+  <si>
+    <t>TS-011</t>
+  </si>
+  <si>
+    <t>Verify that a user can add a product to the cart</t>
+  </si>
+  <si>
+    <t>1. Select a product. 2. Click Add to Cart. 3. Open the cart.</t>
+  </si>
+  <si>
+    <t>Any available product</t>
+  </si>
+  <si>
+    <t>The selected product should appear in the cart with the correct name, price, and quantity.</t>
+  </si>
+  <si>
+    <t>The selected product was added to the cart with the correct name, price, and quantity.</t>
+  </si>
+  <si>
+    <t>TC-020</t>
+  </si>
+  <si>
+    <t>Verify that a user can remove a product from the cart</t>
+  </si>
+  <si>
+    <t>Cart contains at least one product</t>
+  </si>
+  <si>
+    <t>1. Open the cart. 2. Click Remove for a product. 3. Check the cart contents.</t>
+  </si>
+  <si>
+    <t>One product in the cart</t>
+  </si>
+  <si>
+    <t>The selected product should be removed from the cart, and the cart total should update.</t>
+  </si>
+  <si>
+    <t>The selected product was removed from the cart, and the cart total was updated correctly.</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>TS-012</t>
+  </si>
+  <si>
+    <t>Verify that a user can increase a product's quantity</t>
+  </si>
+  <si>
+    <t>Cart contains a product with available stock</t>
+  </si>
+  <si>
+    <t>1. Open the cart. 2. Click the plus button or increase the quantity. 3. Observe the quantity and subtotal.</t>
+  </si>
+  <si>
+    <t>Initial quantity: 1</t>
+  </si>
+  <si>
+    <t>The quantity should increase by one, and the subtotal should update correctly.</t>
+  </si>
+  <si>
+    <t>The product quantity increased by one, and the subtotal was updated correctly.</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>Verify that a user can decrease a product's quantity</t>
+  </si>
+  <si>
+    <t>Cart contains a product with quantity greater than 1</t>
+  </si>
+  <si>
+    <t>1. Open the cart. 2. Decrease the product quantity by one. 3. Observe the quantity and subtotal.</t>
+  </si>
+  <si>
+    <t>Initial quantity: 2</t>
+  </si>
+  <si>
+    <t>The quantity should decrease by one, and the subtotal should update correctly.</t>
+  </si>
+  <si>
+    <t>The product quantity decreased by one, and the subtotal was updated correctly.</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>Verify that a product quantity cannot be reduced below the minimum</t>
+  </si>
+  <si>
+    <t>Cart contains a product with quantity 1</t>
+  </si>
+  <si>
+    <t>1. Open the cart. 2. Attempt to decrease the quantity below 1. 3. Observe the result.</t>
+  </si>
+  <si>
+    <t>Quantity: 1</t>
+  </si>
+  <si>
+    <t>Quantity should not become zero or negative. If decreasing from 1 removes the item, that behavior should be documented and assessed against the intended requirement.</t>
+  </si>
+  <si>
+    <t>The product quantity did not become zero or negative</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>TC-025</t>
+  </si>
+  <si>
+    <t>TC-026</t>
+  </si>
+  <si>
+    <t>TC-027</t>
+  </si>
+  <si>
+    <t>Verify that product quantity cannot exceed the allowed stock</t>
+  </si>
+  <si>
+    <t>Cart contains a product with a known stock limit</t>
+  </si>
+  <si>
+    <t>1. Open the cart. 2. Increase quantity until the stock limit is reached. 3. Attempt to increase it again.</t>
+  </si>
+  <si>
+    <t>Product stock limit: use the actual stock value shown or configured in ShopEase</t>
+  </si>
+  <si>
+    <t>Quantity should not exceed the available stock.</t>
+  </si>
+  <si>
+    <t>The product quantity did not exceed the available stock limit.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,6 +747,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -631,7 +778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -644,6 +791,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -959,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
@@ -1413,7 +1566,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="86.4">
+    <row r="17" spans="1:10" ht="86.4">
       <c r="A17" s="2" t="s">
         <v>96</v>
       </c>
@@ -1442,7 +1595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="86.4">
+    <row r="18" spans="1:10" ht="86.4">
       <c r="A18" s="2" t="s">
         <v>103</v>
       </c>
@@ -1471,7 +1624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="100.8">
+    <row r="19" spans="1:10" ht="100.8">
       <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
@@ -1500,7 +1653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="115.2">
+    <row r="20" spans="1:10" ht="115.2">
       <c r="A20" s="2" t="s">
         <v>114</v>
       </c>
@@ -1529,7 +1682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="115.2">
+    <row r="21" spans="1:10" ht="115.2">
       <c r="A21" s="2" t="s">
         <v>120</v>
       </c>
@@ -1558,55 +1711,230 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+    <row r="22" spans="1:10">
+      <c r="A22" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" t="s">
+        <v>148</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" t="s">
+        <v>151</v>
+      </c>
+      <c r="E24" t="s">
+        <v>152</v>
+      </c>
+      <c r="F24" t="s">
+        <v>153</v>
+      </c>
+      <c r="G24" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24" t="s">
+        <v>155</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" t="s">
+        <v>162</v>
+      </c>
+      <c r="H25" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" t="s">
+        <v>166</v>
+      </c>
+      <c r="E26" t="s">
+        <v>167</v>
+      </c>
+      <c r="F26" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" t="s">
+        <v>169</v>
+      </c>
+      <c r="H26" t="s">
+        <v>170</v>
+      </c>
+      <c r="I26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" t="s">
+        <v>174</v>
+      </c>
+      <c r="F27" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" t="s">
+        <v>177</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>182</v>
+      </c>
+      <c r="D28" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" t="s">
+        <v>184</v>
+      </c>
+      <c r="F28" t="s">
+        <v>185</v>
+      </c>
+      <c r="G28" t="s">
+        <v>186</v>
+      </c>
+      <c r="H28" t="s">
+        <v>187</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>179</v>
+      </c>
+      <c r="I29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>180</v>
+      </c>
+      <c r="I30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>181</v>
+      </c>
+      <c r="I31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="I32" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A22:J22"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B3B503-3D02-487C-A29A-F425B79149E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28BC319-4D27-4881-9001-66F637354708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="214">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -618,9 +618,6 @@
     <t>Cart contains at least one product</t>
   </si>
   <si>
-    <t>1. Open the cart. 2. Click Remove for a product. 3. Check the cart contents.</t>
-  </si>
-  <si>
     <t>One product in the cart</t>
   </si>
   <si>
@@ -642,9 +639,6 @@
     <t>Cart contains a product with available stock</t>
   </si>
   <si>
-    <t>1. Open the cart. 2. Click the plus button or increase the quantity. 3. Observe the quantity and subtotal.</t>
-  </si>
-  <si>
     <t>Initial quantity: 1</t>
   </si>
   <si>
@@ -663,9 +657,6 @@
     <t>Cart contains a product with quantity greater than 1</t>
   </si>
   <si>
-    <t>1. Open the cart. 2. Decrease the product quantity by one. 3. Observe the quantity and subtotal.</t>
-  </si>
-  <si>
     <t>Initial quantity: 2</t>
   </si>
   <si>
@@ -684,9 +675,6 @@
     <t>Cart contains a product with quantity 1</t>
   </si>
   <si>
-    <t>1. Open the cart. 2. Attempt to decrease the quantity below 1. 3. Observe the result.</t>
-  </si>
-  <si>
     <t>Quantity: 1</t>
   </si>
   <si>
@@ -714,9 +702,6 @@
     <t>Cart contains a product with a known stock limit</t>
   </si>
   <si>
-    <t>1. Open the cart. 2. Increase quantity until the stock limit is reached. 3. Attempt to increase it again.</t>
-  </si>
-  <si>
     <t>Product stock limit: use the actual stock value shown or configured in ShopEase</t>
   </si>
   <si>
@@ -724,13 +709,126 @@
   </si>
   <si>
     <t>The product quantity did not exceed the available stock limit.</t>
+  </si>
+  <si>
+    <t>Verify that the cart handles a quantity exceeding available stock</t>
+  </si>
+  <si>
+    <t>Attempt a quantity greater than the product's stock</t>
+  </si>
+  <si>
+    <t>The application should prevent the excess quantity or display a clear validation message and prevent checkout with an invalid quantity.</t>
+  </si>
+  <si>
+    <t>The application prevented a quantity above available stock and displayed appropriate feedback, if applicable.</t>
+  </si>
+  <si>
+    <t>TS-013</t>
+  </si>
+  <si>
+    <t>Verify that a product subtotal is calculated correctly</t>
+  </si>
+  <si>
+    <t>Cart contains a product</t>
+  </si>
+  <si>
+    <t>Unit price: actual displayed product price, quantity: 2</t>
+  </si>
+  <si>
+    <t>Subtotal should equal unit price multiplied by quantity, subject to any clearly specified discount or pricing rules.</t>
+  </si>
+  <si>
+    <t>The displayed subtotal matched the unit price multiplied by the quantity.</t>
+  </si>
+  <si>
+    <t>Verify that a product discount is calculated correctly</t>
+  </si>
+  <si>
+    <t>A product with a displayed discount is available</t>
+  </si>
+  <si>
+    <t>Use an actual discounted product from ShopEase</t>
+  </si>
+  <si>
+    <t>Discounted price should equal original price minus the discount amount, using the site's rounding rules.</t>
+  </si>
+  <si>
+    <t>The displayed discounted price matched the expected discount calculation.</t>
+  </si>
+  <si>
+    <t>TC-028</t>
+  </si>
+  <si>
+    <t>TS-014</t>
+  </si>
+  <si>
+    <t>Verify that cart items remain after reopening the website</t>
+  </si>
+  <si>
+    <t>ShopEase is open and a product can be added to the cart</t>
+  </si>
+  <si>
+    <t>One product, quantity 1</t>
+  </si>
+  <si>
+    <t>The cart should retain the product and its quantity after reopening the website if persistent cart storage is part of the project requirements.</t>
+  </si>
+  <si>
+    <t>The cart retained the selected product and its quantity after reopening the website.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.    2. Click Remove for a product.                  3. Check the cart contents.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.    2. Click the plus button or increase the quantity.                   3. Observe the quantity and subtotal.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.      2. Decrease the product quantity by one.                                      3. Observe the quantity and subtotal.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.          2. Attempt to decrease the quantity below 1.         3. Observe the result.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.     2. Increase quantity until the stock limit is reached.                     3. Attempt to increase it again.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.    2. Increase the quantity beyond available stock, if possible.                            3. Observe the displayed quantity and any validation message.</t>
+  </si>
+  <si>
+    <t>1. Add a product to the cart.                               2. Note its unit price.                                              3. Set the quantity to 2.                                           4. Compare the displayed subtotal with unit price × quantity.</t>
+  </si>
+  <si>
+    <t>1. Open the discounted product.                                2. Note its original price and discount percentage.                       3. Calculate the discounted price.          4. Compare your calculation with the website price.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Add a product to the cart.                                       2. Note its name and quantity.                       3. Close the browser.                                    4. Reopen </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>index.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.                                    5. Open the cart and check its contents.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1113,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
@@ -1125,7 +1223,7 @@
     <col min="8" max="8" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1157,7 +1255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>63</v>
       </c>
@@ -1171,7 +1269,7 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:13" ht="115.2">
+    <row r="3" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1200,7 +1298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="115.2">
+    <row r="4" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1233,7 +1331,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="115.2">
+    <row r="5" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -1262,7 +1360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="129.6">
+    <row r="6" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1291,7 +1389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="158.4">
+    <row r="7" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -1320,7 +1418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="144">
+    <row r="8" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>44</v>
       </c>
@@ -1349,7 +1447,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="158.4">
+    <row r="9" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
@@ -1378,7 +1476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="172.8">
+    <row r="10" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -1407,7 +1505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>64</v>
       </c>
@@ -1421,7 +1519,7 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="72">
+    <row r="12" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>66</v>
       </c>
@@ -1450,7 +1548,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="72">
+    <row r="13" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
@@ -1479,7 +1577,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="100.8">
+    <row r="14" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -1508,7 +1606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="115.2">
+    <row r="15" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>84</v>
       </c>
@@ -1537,7 +1635,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="72">
+    <row r="16" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
@@ -1566,7 +1664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="86.4">
+    <row r="17" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>96</v>
       </c>
@@ -1595,7 +1693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="86.4">
+    <row r="18" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>103</v>
       </c>
@@ -1624,7 +1722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="100.8">
+    <row r="19" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
@@ -1653,7 +1751,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="115.2">
+    <row r="20" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>114</v>
       </c>
@@ -1682,7 +1780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="115.2">
+    <row r="21" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>120</v>
       </c>
@@ -1711,7 +1809,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>141</v>
       </c>
@@ -1725,206 +1823,293 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
+    <row r="23" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
+      <c r="I23" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="I24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
+      <c r="B25" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="H25" t="s">
+      <c r="B26" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="s">
+      <c r="D26" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="E26" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D26" t="s">
+      <c r="G26" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E26" t="s">
+      <c r="H26" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F26" t="s">
+      <c r="I26" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G26" t="s">
+      <c r="B27" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="H26" t="s">
+      <c r="D27" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="I26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="s">
+      <c r="E27" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="G27" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D27" t="s">
+      <c r="H27" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E27" t="s">
+      <c r="I27" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F27" t="s">
+      <c r="B28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G27" t="s">
+      <c r="B29" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="H27" t="s">
+      <c r="B30" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="I27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>178</v>
-      </c>
-      <c r="B28" t="s">
-        <v>157</v>
-      </c>
-      <c r="C28" t="s">
-        <v>182</v>
-      </c>
-      <c r="D28" t="s">
-        <v>183</v>
-      </c>
-      <c r="E28" t="s">
-        <v>184</v>
-      </c>
-      <c r="F28" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" t="s">
-        <v>186</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="B31" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I29" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>180</v>
-      </c>
-      <c r="I30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>181</v>
-      </c>
-      <c r="I31" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="I32" t="s">
+      <c r="C31" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>18</v>
       </c>
     </row>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28BC319-4D27-4881-9001-66F637354708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BB0893-21BF-4BB4-9AFC-D948E86B7C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="235">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -546,27 +546,9 @@
     <t>1. Search for an existing product using uppercase letters.                      2. Observe the results.</t>
   </si>
   <si>
-    <t>1. Select the rating sort option.                  2. Compare product ratings from top to bottom.</t>
-  </si>
-  <si>
-    <t>1. Open an out-of-stock product.             2. Check its availability.                  3. Attempt to add it to the cart, if the control is available.                  4. Check the cart.</t>
-  </si>
-  <si>
     <t>1. Click a product or its View Details button.                              2. Inspect the product details page.</t>
   </si>
   <si>
-    <t>1. Select Price: High to Low.                                2. Compare the displayed prices from top to bottom.</t>
-  </si>
-  <si>
-    <t>1. Select Price: Low to High.                              2. Compare the displayed prices from top to bottom.</t>
-  </si>
-  <si>
-    <t>1. Enter valid email.   2. Leave Password empty.                          3. Click Login.</t>
-  </si>
-  <si>
-    <t>1. Enter an invalid email.                            2. Enter a valid password.                    3. Click Login.</t>
-  </si>
-  <si>
     <t>1. Enter a password containing 7 characters.                  2. Submit the form.    3. Verify validation.    4. Enter a password containing exactly 8 characters.                  5. Submit the form.    6. Verify validation.</t>
   </si>
   <si>
@@ -582,9 +564,6 @@
     <t>1. Enter a product name that does not exist.                             2. Submit the search.</t>
   </si>
   <si>
-    <t>1. Select a category, such as Electronics.   2. Observe the product listing.</t>
-  </si>
-  <si>
     <t>Cart</t>
   </si>
   <si>
@@ -597,9 +576,6 @@
     <t>Verify that a user can add a product to the cart</t>
   </si>
   <si>
-    <t>1. Select a product. 2. Click Add to Cart. 3. Open the cart.</t>
-  </si>
-  <si>
     <t>Any available product</t>
   </si>
   <si>
@@ -777,32 +753,113 @@
     <t>The cart retained the selected product and its quantity after reopening the website.</t>
   </si>
   <si>
-    <t>1. Open the cart.    2. Click Remove for a product.                  3. Check the cart contents.</t>
-  </si>
-  <si>
-    <t>1. Open the cart.    2. Click the plus button or increase the quantity.                   3. Observe the quantity and subtotal.</t>
-  </si>
-  <si>
-    <t>1. Open the cart.      2. Decrease the product quantity by one.                                      3. Observe the quantity and subtotal.</t>
-  </si>
-  <si>
-    <t>1. Open the cart.          2. Attempt to decrease the quantity below 1.         3. Observe the result.</t>
-  </si>
-  <si>
-    <t>1. Open the cart.     2. Increase quantity until the stock limit is reached.                     3. Attempt to increase it again.</t>
-  </si>
-  <si>
-    <t>1. Open the cart.    2. Increase the quantity beyond available stock, if possible.                            3. Observe the displayed quantity and any validation message.</t>
-  </si>
-  <si>
-    <t>1. Add a product to the cart.                               2. Note its unit price.                                              3. Set the quantity to 2.                                           4. Compare the displayed subtotal with unit price × quantity.</t>
-  </si>
-  <si>
-    <t>1. Open the discounted product.                                2. Note its original price and discount percentage.                       3. Calculate the discounted price.          4. Compare your calculation with the website price.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Add a product to the cart.                                       2. Note its name and quantity.                       3. Close the browser.                                    4. Reopen </t>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>TC-029</t>
+  </si>
+  <si>
+    <t>TC-030</t>
+  </si>
+  <si>
+    <t>TC-031</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>TC-034</t>
+  </si>
+  <si>
+    <t>TC-035</t>
+  </si>
+  <si>
+    <t>TC-036</t>
+  </si>
+  <si>
+    <t>TC-037</t>
+  </si>
+  <si>
+    <t>TC-038</t>
+  </si>
+  <si>
+    <t>TC-039</t>
+  </si>
+  <si>
+    <t>TC-040</t>
+  </si>
+  <si>
+    <t>TC-041</t>
+  </si>
+  <si>
+    <t>TC-042</t>
+  </si>
+  <si>
+    <t>TS-015</t>
+  </si>
+  <si>
+    <t>Verify that a user can complete checkout with valid information</t>
+  </si>
+  <si>
+    <t>Order should be placed successfully and the order success page should be displayed.</t>
+  </si>
+  <si>
+    <t>The order was placed successfully, and the order success page was displayed.</t>
+  </si>
+  <si>
+    <t>1. Enter valid email.                 2. Leave Password empty.                          3. Click Login.</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid email.                            2. Enter a valid password.                                       3. Click Login.</t>
+  </si>
+  <si>
+    <t>1. Select a category, such as Electronics.             2. Observe the product listing.</t>
+  </si>
+  <si>
+    <t>1. Select Price: Low to High.                                                   2. Compare the displayed prices from top to bottom.</t>
+  </si>
+  <si>
+    <t>1. Select Price: High to Low.                                                    2. Compare the displayed prices from top to bottom.</t>
+  </si>
+  <si>
+    <t>1. Select the rating sort option.                                               2. Compare product ratings from top to bottom.</t>
+  </si>
+  <si>
+    <t>1. Open an out-of-stock product.                                               2. Check its availability.                  3. Attempt to add it to the cart, if the control is available.                                        4. Check the cart.</t>
+  </si>
+  <si>
+    <t>1. Select a product.                          2. Click Add to Cart.                        3. Open the cart.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.                                2. Click Remove for a product.                                             3. Check the cart contents.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.                                          2. Click the plus button or increase the quantity.                   3. Observe the quantity and subtotal.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.                              2. Decrease the product quantity by one.                                      3. Observe the quantity and subtotal.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.                            2. Attempt to decrease the quantity below 1.         3. Observe the result.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.                           2. Increase quantity until the stock limit is reached.                     3. Attempt to increase it again.</t>
+  </si>
+  <si>
+    <t>1. Open the cart.                                2. Increase the quantity beyond available stock, if possible.                                                          3. Observe the displayed quantity and any validation message.</t>
+  </si>
+  <si>
+    <t>1. Add a product to the cart.                                                2. Note its unit price.                                              3. Set the quantity to 2.                                           4. Compare the displayed subtotal with unit price × quantity.</t>
+  </si>
+  <si>
+    <t>1. Open the discounted product.                                          2. Note its original price and discount percentage.                                     3. Calculate the discounted price.                         4. Compare your calculation with the website price.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Add a product to the cart.                                                       2. Note its name and quantity.                                                 3. Close the browser.                                    4. Reopen </t>
     </r>
     <r>
       <rPr>
@@ -821,6 +878,122 @@
         <scheme val="minor"/>
       </rPr>
       <t>.                                    5. Open the cart and check its contents.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Open the cart.                           2. Click Proceed to Checkout.                                          3. Enter valid full name, email, phone, address, city, and postal code.                                          4. Select Cash on Delivery.                                                   5. Submit the order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Name: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Kasun Perera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Email: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>kasun@example.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Phone: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0771234567</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Address: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">25 Main Street                             </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> City: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Colombo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Postal code: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>12345</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Payment Cash on Delivery</t>
     </r>
   </si>
 </sst>
@@ -876,7 +1049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -890,11 +1063,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1210,17 +1389,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="30.5546875" customWidth="1"/>
     <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" customWidth="1"/>
+    <col min="7" max="7" width="26.33203125" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1360,7 +1539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1374,7 +1553,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>36</v>
@@ -1389,7 +1568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -1403,7 +1582,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>41</v>
@@ -1461,7 +1640,7 @@
         <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>53</v>
@@ -1490,7 +1669,7 @@
         <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>58</v>
@@ -1533,7 +1712,7 @@
         <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>70</v>
@@ -1562,7 +1741,7 @@
         <v>75</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
@@ -1591,7 +1770,7 @@
         <v>75</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>83</v>
@@ -1635,7 +1814,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
@@ -1649,7 +1828,7 @@
         <v>92</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>140</v>
+        <v>218</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -1664,7 +1843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>96</v>
       </c>
@@ -1678,7 +1857,7 @@
         <v>99</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>100</v>
@@ -1693,7 +1872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>103</v>
       </c>
@@ -1707,7 +1886,7 @@
         <v>99</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>131</v>
+        <v>220</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>105</v>
@@ -1722,7 +1901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
@@ -1736,7 +1915,7 @@
         <v>110</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>111</v>
@@ -1765,7 +1944,7 @@
         <v>75</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>117</v>
@@ -1780,7 +1959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>120</v>
       </c>
@@ -1794,7 +1973,7 @@
         <v>123</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>129</v>
+        <v>222</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>124</v>
@@ -1810,275 +1989,275 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-    </row>
-    <row r="23" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="I24" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E25" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="I25" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="E26" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="I26" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="E27" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="I27" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="E31" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>18</v>
@@ -2086,38 +2265,147 @@
     </row>
     <row r="32" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+    </row>
+    <row r="34" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B34" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>199</v>
       </c>
-      <c r="C32" s="2" t="s">
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>200</v>
       </c>
-      <c r="D32" s="2" t="s">
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>201</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F32" s="2" t="s">
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>202</v>
       </c>
-      <c r="G32" s="2" t="s">
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>203</v>
       </c>
-      <c r="H32" s="2" t="s">
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>204</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>18</v>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BB0893-21BF-4BB4-9AFC-D948E86B7C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA7C041-FAE7-429C-8924-1333CDE07A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="305">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -995,6 +995,306 @@
       </rPr>
       <t xml:space="preserve"> Payment Cash on Delivery</t>
     </r>
+  </si>
+  <si>
+    <t>TS-016</t>
+  </si>
+  <si>
+    <t>Verify validation when full name is empty</t>
+  </si>
+  <si>
+    <t>Checkout page is open and cart contains a product</t>
+  </si>
+  <si>
+    <t>1. Leave Full Name empty. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>Full Name: empty; other fields: valid</t>
+  </si>
+  <si>
+    <t>Order should not be submitted. A required-field validation message should appear for Full Name.</t>
+  </si>
+  <si>
+    <t>Order submission was prevented, and a validation message was displayed for Full Name.</t>
+  </si>
+  <si>
+    <t>Verify validation when email is empty</t>
+  </si>
+  <si>
+    <t>1. Enter a valid full name. 2. Leave Email empty. 3. Complete the other required fields correctly. 4. Select Cash on Delivery. 5. Submit the order.</t>
+  </si>
+  <si>
+    <t>Email: empty; other fields: valid</t>
+  </si>
+  <si>
+    <t>Order should not be submitted. An email-required validation message should appear.</t>
+  </si>
+  <si>
+    <t>Order submission was prevented, and the email-required validation message was displayed.</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid email address. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Email: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>kasun@</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; other fields: valid</t>
+    </r>
+  </si>
+  <si>
+    <t>Order should not be submitted. A clear invalid-email validation message should appear.</t>
+  </si>
+  <si>
+    <t>Order submission was prevented, and an invalid-email validation message was displayed.</t>
+  </si>
+  <si>
+    <t>TS-017</t>
+  </si>
+  <si>
+    <t>Verify validation when the phone number contains letters or invalid characters</t>
+  </si>
+  <si>
+    <t>1. Enter a phone number containing letters. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phone: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>077ABC1234</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; other fields: valid</t>
+    </r>
+  </si>
+  <si>
+    <t>Invalid phone input should be rejected, and an appropriate validation message should appear.</t>
+  </si>
+  <si>
+    <t>The invalid phone number was rejected, and a validation message was displayed.</t>
+  </si>
+  <si>
+    <t>Verify phone validation with a 9-digit number</t>
+  </si>
+  <si>
+    <t>1. Enter a 9-digit phone number. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phone: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>771234567</t>
+    </r>
+  </si>
+  <si>
+    <t>The 9-digit number should be rejected if the application's requirement is exactly 10 digits.</t>
+  </si>
+  <si>
+    <t>The 9-digit phone number was rejected, and a validation message was displayed.</t>
+  </si>
+  <si>
+    <t>Verify phone validation with a 10-digit number</t>
+  </si>
+  <si>
+    <t>1. Enter a 10-digit phone number. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phone: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0771234567</t>
+    </r>
+  </si>
+  <si>
+    <t>The 10-digit number should be accepted if it meets the application's phone format rules.</t>
+  </si>
+  <si>
+    <t>The 10-digit phone number was accepted.</t>
+  </si>
+  <si>
+    <t>Verify phone validation with an 11-digit number</t>
+  </si>
+  <si>
+    <t>1. Enter an 11-digit phone number. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phone: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>07712345678</t>
+    </r>
+  </si>
+  <si>
+    <t>The 11-digit number should be rejected if the application's requirement is exactly 10 digits.</t>
+  </si>
+  <si>
+    <t>The 11-digit phone number was rejected, and a validation message was displayed.</t>
+  </si>
+  <si>
+    <t>Verify validation when address is empty</t>
+  </si>
+  <si>
+    <t>1. Leave Address empty. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>Address: empty; other fields: valid</t>
+  </si>
+  <si>
+    <t>Order should not be submitted, and an address-required validation message should appear.</t>
+  </si>
+  <si>
+    <t>Order submission was prevented, and an address-required validation message was displayed.</t>
+  </si>
+  <si>
+    <t>Verify validation when city is empty</t>
+  </si>
+  <si>
+    <t>1. Leave City empty. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>City: empty; other fields: valid</t>
+  </si>
+  <si>
+    <t>Order should not be submitted, and a city-required validation message should appear.</t>
+  </si>
+  <si>
+    <t>Order submission was prevented, and a city-required validation message was displayed.</t>
+  </si>
+  <si>
+    <t>TS-018</t>
+  </si>
+  <si>
+    <t>Verify validation when postal code contains letters or an invalid format</t>
+  </si>
+  <si>
+    <t>1. Enter a postal code containing letters. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Postal code: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>12AB5</t>
+    </r>
+  </si>
+  <si>
+    <t>The invalid postal code should be rejected, and an appropriate validation message should appear.</t>
+  </si>
+  <si>
+    <t>The invalid postal code was rejected, and a validation message was displayed.</t>
+  </si>
+  <si>
+    <t>Verify validation with a 5-digit postal code</t>
+  </si>
+  <si>
+    <t>1. Enter a 5-digit postal code. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Postal code: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>12345</t>
+    </r>
+  </si>
+  <si>
+    <t>The 5-digit postal code should be accepted if the application requires exactly 5 digits.</t>
+  </si>
+  <si>
+    <t>The 5-digit postal code was accepted.</t>
+  </si>
+  <si>
+    <t>TS-019</t>
+  </si>
+  <si>
+    <t>Verify validation when no payment method is selected</t>
+  </si>
+  <si>
+    <t>1. Fill all required customer fields correctly. 2. Do not select a payment method. 3. Submit the order.</t>
+  </si>
+  <si>
+    <t>Payment method: none; other fields: valid</t>
+  </si>
+  <si>
+    <t>Order should not be submitted, and a payment-method-required message should appear, if selecting a method is mandatory.</t>
+  </si>
+  <si>
+    <t>Order submission was prevented because no payment method was selected.</t>
+  </si>
+  <si>
+    <t>Verify that checkout succeeds when Cash on Delivery is selected</t>
+  </si>
+  <si>
+    <t>Cart contains at least one product, and checkout page is open</t>
+  </si>
+  <si>
+    <t>1. Enter valid customer information. 2. Select Cash on Delivery. 3. Submit the order. 4. Observe the confirmation page.</t>
+  </si>
+  <si>
+    <t>Valid customer details; Payment: Cash on Delivery</t>
+  </si>
+  <si>
+    <t>The order should be placed successfully, and an order confirmation or success page should appear.</t>
+  </si>
+  <si>
+    <t>The order was placed successfully using Cash on Delivery, and the confirmation page was displayed.</t>
   </si>
 </sst>
 </file>
@@ -2339,65 +2639,377 @@
       <c r="A35" t="s">
         <v>199</v>
       </c>
+      <c r="B35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D35" t="s">
+        <v>237</v>
+      </c>
+      <c r="E35" t="s">
+        <v>238</v>
+      </c>
+      <c r="F35" t="s">
+        <v>239</v>
+      </c>
+      <c r="G35" t="s">
+        <v>240</v>
+      </c>
+      <c r="H35" t="s">
+        <v>241</v>
+      </c>
+      <c r="I35" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>200</v>
       </c>
+      <c r="B36" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" t="s">
+        <v>243</v>
+      </c>
+      <c r="F36" t="s">
+        <v>244</v>
+      </c>
+      <c r="G36" t="s">
+        <v>245</v>
+      </c>
+      <c r="H36" t="s">
+        <v>246</v>
+      </c>
+      <c r="I36" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>201</v>
       </c>
+      <c r="B37" t="s">
+        <v>235</v>
+      </c>
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E37" t="s">
+        <v>247</v>
+      </c>
+      <c r="F37" t="s">
+        <v>248</v>
+      </c>
+      <c r="G37" t="s">
+        <v>249</v>
+      </c>
+      <c r="H37" t="s">
+        <v>250</v>
+      </c>
+      <c r="I37" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>202</v>
       </c>
+      <c r="B38" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" t="s">
+        <v>252</v>
+      </c>
+      <c r="D38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E38" t="s">
+        <v>253</v>
+      </c>
+      <c r="F38" t="s">
+        <v>254</v>
+      </c>
+      <c r="G38" t="s">
+        <v>255</v>
+      </c>
+      <c r="H38" t="s">
+        <v>256</v>
+      </c>
+      <c r="I38" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>203</v>
       </c>
+      <c r="B39" t="s">
+        <v>251</v>
+      </c>
+      <c r="C39" t="s">
+        <v>257</v>
+      </c>
+      <c r="D39" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" t="s">
+        <v>258</v>
+      </c>
+      <c r="F39" t="s">
+        <v>259</v>
+      </c>
+      <c r="G39" t="s">
+        <v>260</v>
+      </c>
+      <c r="H39" t="s">
+        <v>261</v>
+      </c>
+      <c r="I39" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>204</v>
       </c>
+      <c r="B40" t="s">
+        <v>251</v>
+      </c>
+      <c r="C40" t="s">
+        <v>262</v>
+      </c>
+      <c r="D40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" t="s">
+        <v>263</v>
+      </c>
+      <c r="F40" t="s">
+        <v>264</v>
+      </c>
+      <c r="G40" t="s">
+        <v>265</v>
+      </c>
+      <c r="H40" t="s">
+        <v>266</v>
+      </c>
+      <c r="I40" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>205</v>
       </c>
+      <c r="B41" t="s">
+        <v>251</v>
+      </c>
+      <c r="C41" t="s">
+        <v>267</v>
+      </c>
+      <c r="D41" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" t="s">
+        <v>268</v>
+      </c>
+      <c r="F41" t="s">
+        <v>269</v>
+      </c>
+      <c r="G41" t="s">
+        <v>270</v>
+      </c>
+      <c r="H41" t="s">
+        <v>271</v>
+      </c>
+      <c r="I41" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>206</v>
       </c>
+      <c r="B42" t="s">
+        <v>235</v>
+      </c>
+      <c r="C42" t="s">
+        <v>272</v>
+      </c>
+      <c r="D42" t="s">
+        <v>237</v>
+      </c>
+      <c r="E42" t="s">
+        <v>273</v>
+      </c>
+      <c r="F42" t="s">
+        <v>274</v>
+      </c>
+      <c r="G42" t="s">
+        <v>275</v>
+      </c>
+      <c r="H42" t="s">
+        <v>276</v>
+      </c>
+      <c r="I42" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>207</v>
       </c>
+      <c r="B43" t="s">
+        <v>235</v>
+      </c>
+      <c r="C43" t="s">
+        <v>277</v>
+      </c>
+      <c r="D43" t="s">
+        <v>237</v>
+      </c>
+      <c r="E43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F43" t="s">
+        <v>279</v>
+      </c>
+      <c r="G43" t="s">
+        <v>280</v>
+      </c>
+      <c r="H43" t="s">
+        <v>281</v>
+      </c>
+      <c r="I43" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>208</v>
       </c>
+      <c r="B44" t="s">
+        <v>282</v>
+      </c>
+      <c r="C44" t="s">
+        <v>283</v>
+      </c>
+      <c r="D44" t="s">
+        <v>237</v>
+      </c>
+      <c r="E44" t="s">
+        <v>284</v>
+      </c>
+      <c r="F44" t="s">
+        <v>285</v>
+      </c>
+      <c r="G44" t="s">
+        <v>286</v>
+      </c>
+      <c r="H44" t="s">
+        <v>287</v>
+      </c>
+      <c r="I44" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>209</v>
       </c>
+      <c r="B45" t="s">
+        <v>282</v>
+      </c>
+      <c r="C45" t="s">
+        <v>288</v>
+      </c>
+      <c r="D45" t="s">
+        <v>237</v>
+      </c>
+      <c r="E45" t="s">
+        <v>289</v>
+      </c>
+      <c r="F45" t="s">
+        <v>290</v>
+      </c>
+      <c r="G45" t="s">
+        <v>291</v>
+      </c>
+      <c r="H45" t="s">
+        <v>292</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>210</v>
       </c>
+      <c r="B46" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" t="s">
+        <v>294</v>
+      </c>
+      <c r="D46" t="s">
+        <v>237</v>
+      </c>
+      <c r="E46" t="s">
+        <v>295</v>
+      </c>
+      <c r="F46" t="s">
+        <v>296</v>
+      </c>
+      <c r="G46" t="s">
+        <v>297</v>
+      </c>
+      <c r="H46" t="s">
+        <v>298</v>
+      </c>
+      <c r="I46" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>211</v>
+      </c>
+      <c r="B47" t="s">
+        <v>293</v>
+      </c>
+      <c r="C47" t="s">
+        <v>299</v>
+      </c>
+      <c r="D47" t="s">
+        <v>300</v>
+      </c>
+      <c r="E47" t="s">
+        <v>301</v>
+      </c>
+      <c r="F47" t="s">
+        <v>302</v>
+      </c>
+      <c r="G47" t="s">
+        <v>303</v>
+      </c>
+      <c r="H47" t="s">
+        <v>304</v>
+      </c>
+      <c r="I47" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA7C041-FAE7-429C-8924-1333CDE07A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F032BA-306D-415A-BBA0-EFAA78DCC985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1033,9 +1033,6 @@
     <t>Order submission was prevented, and the email-required validation message was displayed.</t>
   </si>
   <si>
-    <t>1. Enter an invalid email address. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Email: </t>
     </r>
@@ -1071,9 +1068,6 @@
     <t>Verify validation when the phone number contains letters or invalid characters</t>
   </si>
   <si>
-    <t>1. Enter a phone number containing letters. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Phone: </t>
     </r>
@@ -1106,9 +1100,6 @@
     <t>Verify phone validation with a 9-digit number</t>
   </si>
   <si>
-    <t>1. Enter a 9-digit phone number. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Phone: </t>
     </r>
@@ -1131,9 +1122,6 @@
     <t>Verify phone validation with a 10-digit number</t>
   </si>
   <si>
-    <t>1. Enter a 10-digit phone number. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Phone: </t>
     </r>
@@ -1156,9 +1144,6 @@
     <t>Verify phone validation with an 11-digit number</t>
   </si>
   <si>
-    <t>1. Enter an 11-digit phone number. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Phone: </t>
     </r>
@@ -1181,9 +1166,6 @@
     <t>Verify validation when address is empty</t>
   </si>
   <si>
-    <t>1. Leave Address empty. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <t>Address: empty; other fields: valid</t>
   </si>
   <si>
@@ -1196,9 +1178,6 @@
     <t>Verify validation when city is empty</t>
   </si>
   <si>
-    <t>1. Leave City empty. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <t>City: empty; other fields: valid</t>
   </si>
   <si>
@@ -1214,9 +1193,6 @@
     <t>Verify validation when postal code contains letters or an invalid format</t>
   </si>
   <si>
-    <t>1. Enter a postal code containing letters. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Postal code: </t>
     </r>
@@ -1239,9 +1215,6 @@
     <t>Verify validation with a 5-digit postal code</t>
   </si>
   <si>
-    <t>1. Enter a 5-digit postal code. 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Postal code: </t>
     </r>
@@ -1267,9 +1240,6 @@
     <t>Verify validation when no payment method is selected</t>
   </si>
   <si>
-    <t>1. Fill all required customer fields correctly. 2. Do not select a payment method. 3. Submit the order.</t>
-  </si>
-  <si>
     <t>Payment method: none; other fields: valid</t>
   </si>
   <si>
@@ -1285,9 +1255,6 @@
     <t>Cart contains at least one product, and checkout page is open</t>
   </si>
   <si>
-    <t>1. Enter valid customer information. 2. Select Cash on Delivery. 3. Submit the order. 4. Observe the confirmation page.</t>
-  </si>
-  <si>
     <t>Valid customer details; Payment: Cash on Delivery</t>
   </si>
   <si>
@@ -1295,13 +1262,46 @@
   </si>
   <si>
     <t>The order was placed successfully using Cash on Delivery, and the confirmation page was displayed.</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid email address.                                        2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Enter a phone number containing letters.                   2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Enter a 9-digit phone number.                                           2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Enter a 10-digit phone number.                                                   2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Enter an 11-digit phone number.                                                 2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Leave Address empty.                  2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Leave City empty.                          2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Enter a postal code containing letters.                             2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Enter a 5-digit postal code.                                                            2. Complete the other required fields correctly. 3. Select Cash on Delivery. 4. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Fill all required customer fields correctly. 2. Do not select a payment method.                                          3. Submit the order.</t>
+  </si>
+  <si>
+    <t>1. Enter valid customer information.                                      2. Select Cash on Delivery. 3. Submit the order.                        4. Observe the confirmation page.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1689,8 +1689,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M48"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
@@ -1702,7 +1702,7 @@
     <col min="8" max="8" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
         <v>63</v>
       </c>
@@ -1748,7 +1748,7 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="115.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="115.2">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1810,7 +1810,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="115.2">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="72">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="100.8">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="144" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="144">
       <c r="A8" s="1" t="s">
         <v>44</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="158.4">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="172.8">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
         <v>64</v>
       </c>
@@ -1998,7 +1998,7 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="72">
       <c r="A12" s="1" t="s">
         <v>66</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="72">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="100.8">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="115.2">
       <c r="A15" s="2" t="s">
         <v>84</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="43.2">
       <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="57.6">
       <c r="A17" s="2" t="s">
         <v>96</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="57.6">
       <c r="A18" s="2" t="s">
         <v>103</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="72">
       <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="115.2">
       <c r="A20" s="2" t="s">
         <v>114</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="100.8">
       <c r="A21" s="2" t="s">
         <v>120</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" s="5" t="s">
         <v>134</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="57.6">
       <c r="A23" s="2" t="s">
         <v>135</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="57.6">
       <c r="A24" s="2" t="s">
         <v>141</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="72">
       <c r="A25" s="2" t="s">
         <v>147</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="72">
       <c r="A26" s="2" t="s">
         <v>154</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="100.8">
       <c r="A27" s="2" t="s">
         <v>160</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="72">
       <c r="A28" s="2" t="s">
         <v>166</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="100.8">
       <c r="A29" s="2" t="s">
         <v>167</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="100.8">
       <c r="A30" s="2" t="s">
         <v>168</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="115.2">
       <c r="A31" s="2" t="s">
         <v>169</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="115.2">
       <c r="A32" s="2" t="s">
         <v>190</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
         <v>197</v>
       </c>
@@ -2606,7 +2606,7 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="115.2">
       <c r="A34" s="2" t="s">
         <v>198</v>
       </c>
@@ -2635,382 +2635,393 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="35" spans="1:10" ht="72">
+      <c r="A35" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="I35" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="I35" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="86.4">
+      <c r="A36" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="I36" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="I36" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="86.4">
+      <c r="A37" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="86.4">
+      <c r="A38" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="I37" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="C38" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D38" t="s">
+      <c r="G38" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="86.4">
+      <c r="A39" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E38" t="s">
-        <v>253</v>
-      </c>
-      <c r="F38" t="s">
-        <v>254</v>
-      </c>
-      <c r="G38" t="s">
-        <v>255</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="E39" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="I38" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>203</v>
-      </c>
-      <c r="B39" t="s">
-        <v>251</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="G39" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D39" t="s">
+      <c r="H39" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="86.4">
+      <c r="A40" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E39" t="s">
-        <v>258</v>
-      </c>
-      <c r="F39" t="s">
-        <v>259</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="E40" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="H39" t="s">
+      <c r="G40" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="I39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>204</v>
-      </c>
-      <c r="B40" t="s">
-        <v>251</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="H40" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D40" t="s">
+      <c r="I40" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="86.4">
+      <c r="A41" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E40" t="s">
-        <v>263</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E41" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G41" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H41" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="I40" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>205</v>
-      </c>
-      <c r="B41" t="s">
-        <v>251</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="I41" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="72">
+      <c r="A42" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G42" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H42" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I42" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="72">
+      <c r="A43" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="I41" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>206</v>
-      </c>
-      <c r="B42" t="s">
-        <v>235</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="D43" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D42" t="s">
+      <c r="G43" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="86.4">
+      <c r="A44" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E42" t="s">
-        <v>273</v>
-      </c>
-      <c r="F42" t="s">
-        <v>274</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="E44" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="86.4">
+      <c r="A45" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="H42" t="s">
-        <v>276</v>
-      </c>
-      <c r="I42" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>207</v>
-      </c>
-      <c r="B43" t="s">
-        <v>235</v>
-      </c>
-      <c r="C43" t="s">
-        <v>277</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C45" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E43" t="s">
-        <v>278</v>
-      </c>
-      <c r="F43" t="s">
-        <v>279</v>
-      </c>
-      <c r="G43" t="s">
-        <v>280</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="E45" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="I43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>208</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="G45" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C44" t="s">
+      <c r="H45" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D44" t="s">
+      <c r="I45" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="72">
+      <c r="A46" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E46" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="86.4">
+      <c r="A47" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F44" t="s">
-        <v>285</v>
-      </c>
-      <c r="G44" t="s">
-        <v>286</v>
-      </c>
-      <c r="H44" t="s">
-        <v>287</v>
-      </c>
-      <c r="I44" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>209</v>
-      </c>
-      <c r="B45" t="s">
-        <v>282</v>
-      </c>
-      <c r="C45" t="s">
-        <v>288</v>
-      </c>
-      <c r="D45" t="s">
-        <v>237</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="C47" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F45" t="s">
+      <c r="D47" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G45" t="s">
+      <c r="E47" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="H45" t="s">
+      <c r="G47" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I45" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>210</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="H47" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C46" t="s">
-        <v>294</v>
-      </c>
-      <c r="D46" t="s">
-        <v>237</v>
-      </c>
-      <c r="E46" t="s">
-        <v>295</v>
-      </c>
-      <c r="F46" t="s">
-        <v>296</v>
-      </c>
-      <c r="G46" t="s">
-        <v>297</v>
-      </c>
-      <c r="H46" t="s">
-        <v>298</v>
-      </c>
-      <c r="I46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>211</v>
-      </c>
-      <c r="B47" t="s">
-        <v>293</v>
-      </c>
-      <c r="C47" t="s">
-        <v>299</v>
-      </c>
-      <c r="D47" t="s">
-        <v>300</v>
-      </c>
-      <c r="E47" t="s">
-        <v>301</v>
-      </c>
-      <c r="F47" t="s">
-        <v>302</v>
-      </c>
-      <c r="G47" t="s">
-        <v>303</v>
-      </c>
-      <c r="H47" t="s">
-        <v>304</v>
-      </c>
-      <c r="I47" t="s">
-        <v>18</v>
-      </c>
+      <c r="I47" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F032BA-306D-415A-BBA0-EFAA78DCC985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CF53B2-E686-4363-8A9B-953B45D40459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="359">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -1295,13 +1295,215 @@
   </si>
   <si>
     <t>1. Enter valid customer information.                                      2. Select Cash on Delivery. 3. Submit the order.                        4. Observe the confirmation page.</t>
+  </si>
+  <si>
+    <t>Profile/Logout</t>
+  </si>
+  <si>
+    <t>TC-043</t>
+  </si>
+  <si>
+    <t>TC-044</t>
+  </si>
+  <si>
+    <t>TC-045</t>
+  </si>
+  <si>
+    <t>TC-046</t>
+  </si>
+  <si>
+    <t>TC-047</t>
+  </si>
+  <si>
+    <t>TC-048</t>
+  </si>
+  <si>
+    <t>TC-049</t>
+  </si>
+  <si>
+    <t>TC-050</t>
+  </si>
+  <si>
+    <t>TS-020</t>
+  </si>
+  <si>
+    <t>Verify that a logged-in user can view their profile</t>
+  </si>
+  <si>
+    <t>User is logged in to ShopEase</t>
+  </si>
+  <si>
+    <t>Registered demo user</t>
+  </si>
+  <si>
+    <t>The profile page should open and display the user's saved information, such as name, email, phone, and address where available.</t>
+  </si>
+  <si>
+    <t>The profile page opened and displayed the user's saved information.</t>
+  </si>
+  <si>
+    <t>Verify that a user can edit their profile name</t>
+  </si>
+  <si>
+    <t>User is logged in and the profile page is open</t>
+  </si>
+  <si>
+    <t>Kasun Perera QA</t>
+  </si>
+  <si>
+    <t>The new name should be saved and displayed correctly.</t>
+  </si>
+  <si>
+    <t>Verify that a user can edit their profile phone number</t>
+  </si>
+  <si>
+    <t>The new phone number should be saved and displayed correctly.</t>
+  </si>
+  <si>
+    <t>The profile phone number was updated and displayed correctly.</t>
+  </si>
+  <si>
+    <t>Verify that a user can edit their profile address</t>
+  </si>
+  <si>
+    <t>Colombo</t>
+  </si>
+  <si>
+    <t>The new address should be saved and displayed correctly.</t>
+  </si>
+  <si>
+    <t>The profile address was updated and displayed correctly.</t>
+  </si>
+  <si>
+    <t>TS-021</t>
+  </si>
+  <si>
+    <t>Verify that profile changes can be saved</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Change the name to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Kasun QA Tester</t>
+    </r>
+  </si>
+  <si>
+    <t>Changes should be saved, and a suitable confirmation message should appear if implemented.</t>
+  </si>
+  <si>
+    <t>Profile changes were saved, and the updated information was displayed.</t>
+  </si>
+  <si>
+    <t>Verify that saved profile information remains after refreshing the page</t>
+  </si>
+  <si>
+    <t>User is logged in and has saved a profile change</t>
+  </si>
+  <si>
+    <t>Previously saved name or address</t>
+  </si>
+  <si>
+    <t>The saved profile information should remain correct after refreshing the page.</t>
+  </si>
+  <si>
+    <t>The saved profile information remained correct after refreshing the page.</t>
+  </si>
+  <si>
+    <t>TS-022</t>
+  </si>
+  <si>
+    <t>Verify that a logged-in user can log out</t>
+  </si>
+  <si>
+    <t>Logged-in demo user</t>
+  </si>
+  <si>
+    <t>The user should be logged out, and protected navigation options such as Profile and Logout should no longer be available as logged-in options.</t>
+  </si>
+  <si>
+    <t>The user was logged out, and logged-in navigation options were no longer displayed.</t>
+  </si>
+  <si>
+    <t>Verify that a logged-out user cannot access a protected page</t>
+  </si>
+  <si>
+    <t>User has logged in and then logged out</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Protected page URL: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pages/profile.html</t>
+    </r>
+  </si>
+  <si>
+    <t>The user should be redirected to the Login page or shown an access-denied message. Protected profile information should not be accessible while logged out.</t>
+  </si>
+  <si>
+    <t>After logout, the protected profile page redirected the user to the Login page</t>
+  </si>
+  <si>
+    <t>1. Click Profile in the navigation bar.                         2. Observe the profile information.</t>
+  </si>
+  <si>
+    <t>1. Change the name.            2. Save the changes.             3. Check the displayed name.</t>
+  </si>
+  <si>
+    <t>1. Change the phone number.                                               2. Save the changes.               3. Check the displayed phone number.</t>
+  </si>
+  <si>
+    <t>1. Change the address. 2. Save the changes.              3. Check the displayed address.</t>
+  </si>
+  <si>
+    <t>1. Change one or more profile fields.                                       2. Click Save.                               3. Observe any confirmation message and the updated information.</t>
+  </si>
+  <si>
+    <t>1. Save a profile change. 2. Refresh the browser page.                                                 3. Check the profile information.</t>
+  </si>
+  <si>
+    <t>1. Click Logout.                                2. Observe the page displayed.                                               3. Check whether logged-in navigation options disappear.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Log out.                                               2. Manually enter the URL of a protected page, such as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pages/profile.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.                             3. Press Enter.                                     4. Observe whether the profile page is accessible.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1349,7 +1551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1374,6 +1576,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1689,8 +1894,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966FA05-33DA-464B-994B-157739AA2D98}">
-  <dimension ref="A1:M48"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:M58"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
@@ -1702,7 +1907,7 @@
     <col min="8" max="8" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1734,7 +1939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>63</v>
       </c>
@@ -1748,7 +1953,7 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:13" ht="115.2">
+    <row r="3" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1777,7 +1982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="115.2">
+    <row r="4" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1810,7 +2015,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="115.2">
+    <row r="5" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -1839,7 +2044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="72">
+    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1868,7 +2073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="100.8">
+    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -1897,7 +2102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="144">
+    <row r="8" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>44</v>
       </c>
@@ -1926,7 +2131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="158.4">
+    <row r="9" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
@@ -1955,7 +2160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="172.8">
+    <row r="10" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -1984,7 +2189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>64</v>
       </c>
@@ -1998,7 +2203,7 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="72">
+    <row r="12" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>66</v>
       </c>
@@ -2027,7 +2232,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="72">
+    <row r="13" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
@@ -2056,7 +2261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="100.8">
+    <row r="14" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
@@ -2085,7 +2290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="115.2">
+    <row r="15" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>84</v>
       </c>
@@ -2114,7 +2319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="43.2">
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
@@ -2143,7 +2348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="57.6">
+    <row r="17" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>96</v>
       </c>
@@ -2172,7 +2377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="57.6">
+    <row r="18" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>103</v>
       </c>
@@ -2201,7 +2406,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="72">
+    <row r="19" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
@@ -2230,7 +2435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="115.2">
+    <row r="20" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>114</v>
       </c>
@@ -2259,7 +2464,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="100.8">
+    <row r="21" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>120</v>
       </c>
@@ -2288,7 +2493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>134</v>
       </c>
@@ -2302,7 +2507,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" ht="57.6">
+    <row r="23" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>135</v>
       </c>
@@ -2331,7 +2536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="57.6">
+    <row r="24" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>141</v>
       </c>
@@ -2360,7 +2565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="72">
+    <row r="25" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>147</v>
       </c>
@@ -2389,7 +2594,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="72">
+    <row r="26" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>154</v>
       </c>
@@ -2418,7 +2623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="100.8">
+    <row r="27" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>160</v>
       </c>
@@ -2447,7 +2652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="72">
+    <row r="28" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>166</v>
       </c>
@@ -2476,7 +2681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="100.8">
+    <row r="29" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>167</v>
       </c>
@@ -2505,7 +2710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="100.8">
+    <row r="30" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>168</v>
       </c>
@@ -2534,7 +2739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="115.2">
+    <row r="31" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>169</v>
       </c>
@@ -2563,7 +2768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="115.2">
+    <row r="32" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>190</v>
       </c>
@@ -2592,7 +2797,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>197</v>
       </c>
@@ -2606,7 +2811,7 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" ht="115.2">
+    <row r="34" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>198</v>
       </c>
@@ -2635,7 +2840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="72">
+    <row r="35" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>199</v>
       </c>
@@ -2664,7 +2869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="86.4">
+    <row r="36" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>200</v>
       </c>
@@ -2693,7 +2898,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="86.4">
+    <row r="37" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>201</v>
       </c>
@@ -2722,7 +2927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="86.4">
+    <row r="38" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>202</v>
       </c>
@@ -2751,7 +2956,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="86.4">
+    <row r="39" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>203</v>
       </c>
@@ -2780,7 +2985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="86.4">
+    <row r="40" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>204</v>
       </c>
@@ -2809,7 +3014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="86.4">
+    <row r="41" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>205</v>
       </c>
@@ -2838,7 +3043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="72">
+    <row r="42" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>206</v>
       </c>
@@ -2867,7 +3072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="72">
+    <row r="43" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>207</v>
       </c>
@@ -2896,7 +3101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="86.4">
+    <row r="44" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>208</v>
       </c>
@@ -2925,7 +3130,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="86.4">
+    <row r="45" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>209</v>
       </c>
@@ -2954,7 +3159,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="72">
+    <row r="46" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>210</v>
       </c>
@@ -2983,7 +3188,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="86.4">
+    <row r="47" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>211</v>
       </c>
@@ -3012,23 +3217,278 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+    </row>
+    <row r="49" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F51" s="9">
+        <v>771234567</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A48:J48"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\E commerce web\-E-Commerce-Demo-Web-Application\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CF53B2-E686-4363-8A9B-953B45D40459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7192D7-06E2-4EE6-AD2B-E6AB0788145C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9262CFC7-4242-49E1-8025-8C0812D5CB61}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="360">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -1497,6 +1497,9 @@
       </rPr>
       <t>.                             3. Press Enter.                                     4. Observe whether the profile page is accessible.</t>
     </r>
+  </si>
+  <si>
+    <t>The profile name was updated and displayed correctly.</t>
   </si>
 </sst>
 </file>
@@ -3282,7 +3285,9 @@
       <c r="G50" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="H50" s="2"/>
+      <c r="H50" s="2" t="s">
+        <v>359</v>
+      </c>
       <c r="I50" s="2" t="s">
         <v>18</v>
       </c>
